--- a/store/May-2026/Mail Attachment/BTC_Report_31-May-2026.xlsx
+++ b/store/May-2026/Mail Attachment/BTC_Report_31-May-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,33 +518,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WTI-20260531-3906032</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>WTI-20260531-3906198</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indiv</t>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RAVINDRA KUMAR</t>
+          <t>MR.VED. PRAKASH [1941]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-31 13:00:00</t>
+          <t>2026-05-16 04:30:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9035429665</t>
+          <t>9718399166</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ravi@tucano.it</t>
+          <t>billings.manesar@wti.co.in</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +558,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yudhveer Singh W04209</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:19:15.760000</t>
+          <t>2026-05-31 14:17:00.287000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -569,7 +573,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Manesar Hub</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,17 +583,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>na</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>na</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>na</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -597,37 +601,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WTI-20260531-3906126</t>
+          <t>WTI-20260531-3906236</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NESTLE TRAVELDESK</t>
+          <t>Sohanpal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nestle India Limited</t>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MR  DEEPAK YADAV</t>
+          <t>MR.RAKESH [10473]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-31 17:30:00</t>
+          <t>2026-05-23 10:30:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9953176848</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>deepak.yadav1@in.nestle.com</t>
+          <t>dispatch.manesar@wti.co.in</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -637,12 +641,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yudhveer Singh W04209</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-31 12:28:12.770000</t>
+          <t>2026-05-31 16:04:46.643000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -652,69 +656,65 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Manesar Hub</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>na</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>na</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Airport - Noida Rate : 1650.00 ] PkgID:[179653]</t>
-        </is>
-      </c>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WTI-20260531-3906150</t>
+          <t>WTI-20260531-3906228</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Sohanpal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phonepe Limited</t>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VIKAS PUNIA</t>
+          <t>MR.ASHOK KUMAR [11807]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-31 19:00:00</t>
+          <t>2026-05-28 12:25:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9818846102</t>
+          <t>9266079595</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>vikas.punia@phonepe.com</t>
+          <t>dispatch.manesar@wti.co.in</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yudhveer Singh W04209</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-31 13:38:09.310000</t>
+          <t>2026-05-31 16:00:57.673000</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -739,69 +739,65 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Manesar Hub</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>128637</t>
+          <t>na</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>na</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MMT00010158213</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Airport Transfers upto 65 Kms Rate : 2350.00 ] PkgID:[210063]</t>
-        </is>
-      </c>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTI-20260531-3905945</t>
+          <t>WTI-20260531-3906196</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>in-fmcabbookingskpmg.com</t>
+          <t>Sohanpal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SIDDHARTH GUPTA</t>
+          <t>MR.NEERA CHAUDHARY [12909]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-31 20:55:00</t>
+          <t>2026-05-29 18:30:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9711022444</t>
+          <t>9266167009</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>siddharthgupta4@kpmg.com</t>
+          <t>billings.manesar@wti.co.in</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -811,12 +807,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yudhveer Singh W04209</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-31 09:59:46.167000</t>
+          <t>2026-05-31 14:14:04.580000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -826,7 +822,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Manesar Hub</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -836,17 +832,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>P : 1717224 T : 03</t>
+          <t>na</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>P : 1717224 T : 03</t>
+          <t>na</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BT2605312143</t>
+          <t>na</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -854,85 +850,2318 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>WTI-20260531-3906200</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MR.NARINDER KUMAR [9260]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:00:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7069150085</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>billings.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:22:05.850000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906186</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MR.GAURAV TRIPATHI [7697]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:00:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8130391350</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>billings.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:02:14.740000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906227</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MR.ROHIT SINGH [4662]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:15:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8826691852</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-31 15:58:21.307000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906190</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MR.AJAYA KUMAR GIRI [3822]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-29 20:00:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9311533831</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>billings.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:07:46.357000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906226</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MR.AYUSH GUPTA [12069]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-29 20:30:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8865042365</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-31 15:54:35.890000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906202</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MR.KRISHAN KUMAR [5283]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-29 21:00:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8130299538</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>billings.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:25:26.500000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906245</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MR.KRISHAN KUMAR [1774]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-30 04:30:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9718321774</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:09:13.103000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906297</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rajneesh Kumar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Honda Motorcycle &amp; scooter India Pvt Ltd.(Tapukara)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MR.SHUTANSHU GUPTA [4713]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-30 07:00:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8295537516</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-31 17:11:47.520000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PAINT TAPUKRA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>512308</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906282</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MR.RAHUL YADAV [12402]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-30 07:00:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7015167597</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:32:36.023000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906222</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MR.ANIL BINJOLA [6553]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-05-30 07:00:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8288024934</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-31 15:51:54.950000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906251</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MR.SANCHARI SINHA ROY [5184]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:00:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9289152864</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:13:13.897000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906275</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MR.AMIT KUMAR [4338]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-05-30 10:00:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9560893392</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:29:45.847000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906262</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MR.VISHAL KOUL [5275]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:00:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6359610048</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:22:16.810000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906267</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sohanpal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Honda Motorcycles and Scooter India Pvt Ltd - Plant</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MR.SATISH KUMAR DHINGRA [2892]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-31 07:00:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>9718374460</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>dispatch.manesar@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-31 16:25:43.350000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Manesar Hub</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906032</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Indiv</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RAVINDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-31 13:00:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9035429665</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ravi@tucano.it</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-31 11:19:15.760000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906126</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NESTLE TRAVELDESK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nestle India Limited</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MR  DEEPAK YADAV</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-31 17:30:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9953176848</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>deepak.yadav1@in.nestle.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-31 12:28:12.770000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Airport - Noida Rate : 1650.00 ] PkgID:[179653]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906298</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reception Two Horizon</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RAMAN KUMAR KAMAT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-31 17:40:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7428601419</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Reception.GGN@cheil.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-31 17:19:45.737000</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906150</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phonepe Limited</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VIKAS PUNIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:00:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9818846102</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>vikas.punia@phonepe.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-31 13:38:09.310000</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>128637</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>MMT00010158213</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Airport Transfers upto 65 Kms Rate : 2350.00 ] PkgID:[210063]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906346</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AMIT NANDWANI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:00:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>9999971062</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>amit.n@cheil.com</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Kunal.Singh</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:04.407000</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906407</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SANDEEP KUMAR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:30:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8864907779</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>kum.sandeep@cheil.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Kunal.Singh</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:25:54.900000</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906337</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SHAMBHAVI</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:00:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8922069833</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Reception.MPD@cheil.com</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:22:13.220000</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906376</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PRANJAL BORDOLOI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:30:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9811168856</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Reception.MPD@cheil.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:46:08.433000</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Non billable</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Non billable</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3905945</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIDDHARTH GUPTA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-31 20:55:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>9711022444</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>siddharthgupta4@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:59:46.167000</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>P : 1717224 T : 03</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>P : 1717224 T : 03</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>BT2605312143</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906377</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JUDGE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>9968044921</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reception.MPD@cheil.com</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:47:45.987000</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Non-Billable.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Non-Billable.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Non-Billable.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906379</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AJAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>9899069290</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Reception.MPD@cheil.com</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:49:05.897000</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Non – Billable</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Non – Billable</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Non – Billable</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906381</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Reception MPD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cheil India Private Limited</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BISWAJIT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:00:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>9899636406</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Reception.MPD@cheil.com</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ashish.Dagoria</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:50:27.430000</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Non-Billable</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WTI-20260531-3906340</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mr Rex Peter</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Limited</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SYED SAJEETH ( LTR )</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-31 22:30:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>9840724768</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>kam.chennai@wti.co.in</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nigam Sharma</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:38:12.233000</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Chennai Hub</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>WTI-20260531-3906140</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>SELF</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>FLSmidth Private Limited</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>DEEPAK</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2026-05-31 23:30:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>9884716661</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>pd-in@flsmidth.com</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Yudhveer Singh W04209</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2026-05-31 13:15:05.263000</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Chennai Hub</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
